--- a/regulatory-compliance/cloud-foundation/9.1/uk-caf/vcf-91-companion-uk-caf.xlsx
+++ b/regulatory-compliance/cloud-foundation/9.1/uk-caf/vcf-91-companion-uk-caf.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="190" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Version 910-20260612-01</t>
+          <t>Version 910-20260623-01</t>
         </is>
       </c>
     </row>
@@ -536,17 +536,16 @@
     </row>
     <row r="9"/>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Disclaimer</t>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Additional Resources</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>This kit is intended to provide general guidance for organizations that are considering Broadcom solutions. The information contained in this document is for educational and informational purposes only. This document is not intended to provide advice and is provided "AS IS." Broadcom makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of the information contained herein. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations.
-This material is provided as is and any express or implied warranties, including, but not limited to, the implied warranties of merchantability and fitness for a particular purpose are disclaimed. In no event shall the copyright holder or contributors be liable for any direct, indirect, incidental, special, exemplary, or consequential damages (including, but not limited to, procurement of substitute goods or services; loss of use, data, or profits; or business interruption) however caused and on any theory of liability, whether in contract, strict liability, or tort (including negligence or otherwise) arising in any way out of the use of this software, even if advised of the possibility of such damage. The provider makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of this sample. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations. You acknowledge that there may be performance or other considerations, and that these examples may make assumptions which may not be valid in your environment or organization.</t>
+          <t>This is one of a library of companion guides that map VMware Cloud Foundation and its advanced services to security and compliance frameworks. For each framework, the guide is published as a spreadsheet, a CSV data file, a Markdown document, and a PDF, together with a Security Configuration Guide crosswalk that identifies the VCF technical hardening settings relevant to that framework. The companion guide library, the VMware Cloud Foundation Security Configuration Guide, and related security documentation, sample scripts, and Q&amp;A are available at https://brcm.tech/vcf-security.</t>
         </is>
       </c>
     </row>
@@ -554,12 +553,28 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>License</t>
+          <t>Disclaimer</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>This kit is intended to provide general guidance for organizations that are considering Broadcom solutions. The information contained in this document is for educational and informational purposes only. This document is not intended to provide advice and is provided "AS IS." Broadcom makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of the information contained herein. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations.
+This material is provided as is and any express or implied warranties, including, but not limited to, the implied warranties of merchantability and fitness for a particular purpose are disclaimed. In no event shall the copyright holder or contributors be liable for any direct, indirect, incidental, special, exemplary, or consequential damages (including, but not limited to, procurement of substitute goods or services; loss of use, data, or profits; or business interruption) however caused and on any theory of liability, whether in contract, strict liability, or tort (including negligence or otherwise) arising in any way out of the use of this software, even if advised of the possibility of such damage. The provider makes no claims, promises, or guarantees about the accuracy, completeness, or adequacy of this sample. Organizations should engage appropriate legal, business, technical, and audit expertise within their specific organization for review of requirements and effectiveness of implementations. You acknowledge that there may be performance or other considerations, and that these examples may make assumptions which may not be valid in your environment or organization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>License</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Copyright (c) CA, Inc. All rights reserved.
 You are hereby granted a non-exclusive, worldwide, royalty-free license under CA, Inc.'s copyrights to use, copy, modify, and distribute this software in source code or binary form for use in connection with CA, Inc. products.
@@ -568,16 +583,16 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Third Party Identifiers and Mappings</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>This document includes regulatory compliance and security control identifiers from external sources as a convenience to end users. This does not constitute endorsement, in either direction.
 There is not a one-to-one mapping of product capabilities to third-party controls. A product capability, or set of capabilities, may be applicable to multiple controls. Conversely, a control may be satisfied with the use of multiple capabilities.
@@ -1467,7 +1482,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -1482,15 +1497,12 @@
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Contributes</t>
+          <t>Not Applicable</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend's Security Services Platform (SSP) organizes inventory assets into a defined hierarchy of region, zone, environment, application, and application tier, classifying them as either critical or regular applications. This hierarchy gives administrators a structured view of which assets support critical business functions and how they relate to each other within the environment.
-Security Explorer's Applications View designates critical applications as high-priority types that receive enhanced security attention and monitoring, providing a focused view of business-critical workloads and their network security posture. The SSP Inventory monitoring function allows administrators to view the infrastructure hierarchy, including regions, zones, and virtual machines, and verify tag assignments for each infrastructure asset.
-The SSP Segmentation Monitoring capability tracks application security posture over time and allows administrators to identify and address security risks surfaced through application monitoring. The SSP also identifies vulnerable workloads that could be exploited for lateral movement, supporting assessment of which assets pose elevated risk to critical business functions. Security Intelligence provides Infrastructure, Environment, and Application Monitoring capabilities that further aid in mapping asset relationships and security posture across the environment.
-The SSP is a centralized repository that maintains the most current organizational IT assets, including servers, software, and network devices along with their configurations. These capabilities contribute to network-layer asset inventory and dependency mapping but do not replace an enterprise asset management system or provide the full business impact analysis and organizational security assessment processes that a TAAS identification program requires.</t>
+          <t>End user activity or process, design decision, or activity out of scope.</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
@@ -2863,11 +2875,12 @@
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>VMware vDefend's Security Intelligence capability, delivered through the Security Services Platform (SSP), provides live network traffic flow visualization and security posture mapping that directly support the creation and maintenance of network architecture diagrams and data flow documentation. While maintaining formal network diagrams is an organizational responsibility, Security Intelligence generates interactive visualizations of network traffic patterns, security group relationships, and Distributed Firewall (DFW) rule coverage that serve as authoritative inputs to those diagrams.
-Security Intelligence collects and displays network flow data through a visualization canvas covering groups, computes, destination ports, and Layer 7 application IDs. The visualization displays network traffic flows with color-coded indicators: red-hued dashed lines for unprotected flows, blue-hued solid lines for blocked flows, and green-hued solid lines for allowed flows. The Flow Details dialog shows completed network flows and the firewall rules in effect associated with each flow, linking observed traffic patterns to the policies governing them. Flow data includes the groups flows belong to, services used, Layer 7 application ID, and FQDN information. Network flow data is analyzed within a 15-minute window for near-real-time security status, and administrators can select a time period parameter to examine historical traffic flow data for architecture documentation.
-Network traffic flows displayed in Security Intelligence are based on DFW rules in effect and observed traffic during the selected period, covering all traffic matching stateful Layer 4 DFW rules using IPv4 or IPv6. This directly supports the control's requirement that architecture diagrams reflect the current network environment and document how traffic flows through it. The Flow Insights Dashboard categorizes network objects into Rules, Groups, Computes, Destination Ports, and Layer 7 Application IDs, providing a structured multi-dimensional view of the environment's traffic architecture. Security Intelligence also monitors network flows between application pairs and tracks Policy Protection Status to indicate which application communication paths are being monitored.
-Security Intelligence generates DFW security policy recommendations for application and environment categories based on analysis of traffic flows over a specified time period. These recommendations, grounded in observed traffic patterns, provide data-driven support for documenting how data flows through the environment and what security controls apply to those flows.
-Network Detection and Response (NDR) extends this visibility by collecting and presenting detection events representing security-relevant activity in the network, helping security analysts understand threat patterns and the paths through which activity traverses the environment.</t>
+          <t>VMware vDefend contributes to generating logical maps of data-sharing relationships through Security Intelligence's visualization and analysis capabilities, though the full scope of this control also requires organizational processes, formal agreements, and documentation outside vDefend's scope.
+Security Intelligence, hosted within the Security Services Platform, performs segmentation analysis that maps discovered unique assets including workloads, groups, IP addresses, DVPGs, segments, tier-0 and tier-1 gateways, infrastructure services, and infrastructure servers. IP addresses are resolved to VMs, and tier-0 and tier-1 information is mapped to corresponding segments, providing a structured view of how workloads and network constructs relate within the NSX environment. Security Intelligence also maintains an inferred infrastructure Classifications table, with each classification in a Not Reviewed state until accepted or modified by an administrator, supporting the development of a reviewed inventory of compute entities.
+The Security Explorer Computes View supports assigning labels to compute entity nodes for organizational and filtering purposes, and label and entity information can be exported to CSV for external documentation. The Applications View enables drill-down into application tiers to view the specific VMs and IP addresses within each tier, providing visibility into how workloads communicate across application boundaries. Together, these capabilities support understanding which workloads share data and across what network paths, which is a building block for generating logical maps of data-sharing relationships.
+The Distributed Firewall (DFW) rule base functions as a network-layer access control defining which workloads are permitted to communicate with each other. The Identity Firewall feature extends this model by enforcing policies based on user identity. Active Directory users and groups can be used as source criteria in Distributed Firewall and Gateway Firewall rules, enabling access control anchored to user group membership rather than workload IP address alone. Identity Firewall rules can be applied to tier-0 or tier-1 gateways using Active Directory group membership as a source criterion for access control decisions.
+Role-based access control within the Security Services Platform restricts who can view and manage these visualizations and flow data. Five roles are defined with differentiated permissions: Enterprise Admin, Auditor, Security Engineer, Security Operator, and Support Bundle Collector.
+Generating formal Interconnection Security Agreements, mapping data-sharing relationships with external parties beyond the network boundary, and maintaining a registry of all parties with whom sensitive data is shared are organizational governance activities outside vDefend's scope.</t>
         </is>
       </c>
       <c r="I28" s="10" t="inlineStr">
@@ -4122,7 +4135,7 @@
 Backup automation through APIs
 VCF exposes backup automation through its APIs, including the RecoveryBackupJobBackupRequest data structure for specifying backup location, protocol, authorization, and database scope, as well as the RecoveryBackupSchedulesUpdateSpec for programmatically managing backup schedules.
 Disaster recovery planning
-For disaster recovery planning, VCF supports application disaster recovery with data replication to a secondary site. Organizations should plan and test disaster recovery strategies regularly to meet their RTO and RPO targets. VCF Operations provides integration with VMware Live Recovery for periodic test runs to validate that existing recovery plans work with the underlying infrastructure and configured RPO limits. Application disaster recovery may result in some data loss during failover depending on the configured RPO.
+For disaster recovery planning, VCF supports application disaster recovery with data replication to a secondary site. Organizations should plan and test disaster recovery strategies regularly to meet their RTO and RPO targets. VCF Operations provides integration with VCF Protection and Recovery for periodic test runs to validate that existing recovery plans work with the underlying infrastructure and configured RPO limits. Application disaster recovery may result in some data loss during failover depending on the configured RPO.
 VCF directly provides the mechanisms for creating recurring backups, managing retention, and supporting RTO/RPO requirements through multiple backup and snapshot methods. However, organizations must establish backup policies, define RTO/RPO targets, schedule regular restore testing, and maintain backup infrastructure such as external storage and third-party backup solutions to fully satisfy this control.</t>
         </is>
       </c>
@@ -4785,7 +4798,7 @@
 Alarm notifications can be configured to send email, SNMP traps, or run scripts on the vCenter host when an alarm triggers. For email notifications to function, Mail settings must be configured in vCenter Settings. PNR requires an administrator email address to be configured during appliance registration with vCenter. Licensing event alerts can also be configured so that licensing administrators receive email notifications when licensing compliance issues occur.
 vSphere Replication supports configurable alarms for replication events. Administrators can define and edit alarms so that specific replication events, such as after configuring a virtual machine for replication, trigger notifications.
 In 9.1, the unified PNR appliance includes the Clean Room Orchestrator, which adds a distinct alerting surface for cyber recovery operations. The Clean Room Orchestrator sends email alerts to configured recipients when the status of recovery environment components changes, such as when the Orchestrator or connector moves from good to warning status. PNR maintains an Alarms list for the clean room showing a history of all notifications requiring attention, with search and filtering by severity. PNR also supports configuration of email alerts for critical events to notify users of important recovery operations and system events.
-The Protection and Recovery Overview Dashboard displays alerts with severity levels of Critical, Immediate, and Warning for snapshots, protection groups, recovery plans, and deployment settings. Through the VMware Live Recovery Cloud Management Pack integration with VCF Operations, administrators receive health alerts for protection groups, recovery plans, cloud file systems, recovery SDDCs, and protected sites.
+The Protection and Recovery Overview Dashboard displays alerts with severity levels of Critical, Immediate, and Warning for snapshots, protection groups, recovery plans, and deployment settings. Through the VCF Protection and Recovery Cloud Management Pack integration with VCF Operations, administrators receive health alerts for protection groups, recovery plans, cloud file systems, recovery SDDCs, and protected sites.
 For environments using PNR's Cyber Recovery capability, PNR supports integration with CrowdStrike, which provides CrowdScore for Incident Detections. CrowdScore measures the real-time threat level to recovery endpoints on a scale of 0 to 100, calculated using factors including frequency, severity, and correlation of security alerts, giving administrators a data protection-scoped view of security conditions relevant to recovery readiness.
 These PNR-native alerting mechanisms contribute to situational awareness for data protection activities. Physical infrastructure alerting, network security alerting, and supply chain alerting fall outside PNR's scope and depend on the broader VCF platform and supplementary tools.</t>
         </is>
@@ -5005,13 +5018,14 @@
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>VCF provides several capabilities that contribute to anomalous behavior detection and user activity monitoring, though it does not include a dedicated User &amp; Entity Behavior Analytics (UEBA) or User Activity Monitoring (UAM) solution.
-VCF Operations includes anomaly detection capabilities that use both dynamic and static thresholds to identify when metrics deviate from normal operating behavior. Dynamic thresholding is enabled by default and uses historical data analysis to establish baselines for each monitored object. The Smart Early Warning feature analyzes the number of applicable metrics that violate the dynamic threshold determining normal operating behavior, triggering alerts when the number of anomalies on an object exceeds a trending threshold. When an anomalous entity is detected, VCF Operations generates an outlier violation alert (vmwAnalyticsOutlierEvent, OID 37002), notifying administrators of unexpected behavior. A Critical threshold violation alert is also generated when anomalous entities are detected.
-The Anomalies widget displays detected anomalies for a resource over the past six hours at configurable time intervals, with color-coded criticality indicators. The Anomaly Breakdown widget shows likely root causes for symptoms on a selected resource, helping operators triage issues. The Troubleshooting Workbench includes an Anomalous Metrics card that surfaces metrics exhibiting drastic changes within a selected scope and time window, ranked by degree of change with the most recent anomaly given the highest weighting. Administrators can also examine outlier VMs detected by VCF Operations to identify unexpected behavior and take corrective actions. VCF Operations supports outbound SNMP trap notifications, enabling alert delivery to external SNMP management systems with up to four configurable trap destinations.
-For user activity monitoring, VCF Operations provides a User Activity Audit report that offers traceability of user actions including logging in, operations on clusters and nodes, changes to system passwords, certificate activation, and logging out. Each audit event has a detailed view containing information that supports analysis of events in the virtual infrastructure for suspicious user actions or system issues. Event auditing across the VCF platform provides visibility into platform interaction changes and surfaces suspicious access events and policy violations. Administrators should continuously monitor user security aspects to detect security risks early and respond to potential threats. VCF SSO maintains a dedicated audit log that captures user management events, including account creation, modification, deletion, and activation or deactivation, as well as changes to account credentials and profile information. The vSphere Client's Advanced Export feature allows administrators to export tasks performed by a specific user during a specified time range, providing targeted audit data for investigating suspicious activity.
-Audit logging extends across VCF components. NSX Manager generates audit log messages that record user operations with fields for UserName, ModuleName, Operation, and Operation status, along with detailed resource change information and timestamps. NSX Manager audit logs also record failed login attempts with username and timestamp information, enabling tracking of access patterns across the environment. VCF Operations for Networks captures audit logs of administrative actions, including CRUD operations and login/logout events.
-VCF Operations supports forwarding user activity audit logs to an external syslog server, enabling integration with dedicated SIEM or UEBA platforms for broader correlation and behavioral analysis. VCF Log Management includes content packs that offer pre-built dashboards, alerts, and queries for VCF components. These content packs support security monitoring use cases such as tracking failed login attempts and privilege escalations.
-VCF's built-in anomaly detection is primarily oriented toward infrastructure metrics and operational health rather than user behavior profiling. A dedicated UEBA or UAM solution consuming VCF's audit data would be needed to establish user behavior baselines, detect credential compromise through behavioral deviation, and provide the full scope of analytics this control requires. For organizations requiring deeper behavioral analysis, VMware vDefend extends VCF's monitoring foundation with IDS/IPS, network traffic inspection, and threat intelligence integration.</t>
+          <t>VCF provides several monitoring, alerting, and network analysis capabilities that contribute to an organization's ability to define and detect Indicators of Compromise (IOC), though fully operationalizing IOC management requires integration with external threat intelligence platforms and organizational processes.
+VCF Operations includes a Security Operations dashboard that provides a consolidated view of the security posture across the managed infrastructure. This dashboard brings together user and infrastructure security elements, helping operators identify areas that might require attention based on security exposure. By centralizing security-relevant telemetry in a single pane, the dashboard supports detection of anomalous conditions that could signal a cybersecurity event.
+VCF Operations continuously monitors infrastructure by evaluating collected data against defined policies. Each object or group receives a compliance score based on how well it adheres to those policies, and alerts are triggered when deviations occur. Organizations can create custom compliance benchmarks that monitor specific alert definitions and policies, allowing security teams to codify their own detection criteria and receive notifications when infrastructure drifts from expected baselines. This policy-based alerting mechanism supports operationalizing certain classes of IOCs, particularly those related to configuration drift, unauthorized changes, or compliance violations.
+VCF Operations supports custom alert definitions that can combine metric-based and log-based symptoms, allowing administrators to define conditions that flag suspicious activity. Alert definitions can incorporate Smart Early Warning conditions and log event patterns from monitored systems. Alert definition Impact settings can be configured to Risk to indicate potential problems that require attention in the near future, providing an early-warning mechanism that organizations can incorporate into incident detection workflows. Problem alerts are logged to syslog, and outbound notification plug-ins (SNMP Trap, webhook, email) allow alerts to be forwarded to external security tools for correlation and triage. VCF Log Management enables log-based symptom definitions that can match patterns across aggregated log data from across the VCF environment.
+At the network layer, NSX provides flow-based observability capabilities. NSX flow queries support filtering and analysis of VTEP traffic, management traffic, and extended L2 network traffic for monitoring and audit purposes. NSX Traceflow provides traffic analysis by specifying source and destination information and returning tables of observed packets. These capabilities help surface unusual communication patterns that organizations can correlate with defined IOCs.
+Log forwarding across VCF components supports IOC operationalization. VMware vCenter, NSX, and VMware ESX hosts can all forward syslog data to external SIEM platforms, where IOC matching and correlation typically occur. NSX audit logs include structured syslog fields that identify security-relevant events, and remote logging can be filtered by severity level and message categories including MONITORING, SECURITY, and SYSTEM.
+For full threat intelligence correlation and signature-based IOC detection, VMware vDefend is a separate product that extends NSX networking with security-specific capabilities: IDS/IPS with support for importing custom and third-party threat intelligence signatures, custom signature bundle management for tailored IOC definitions, Malicious IP Feed integration that downloads known-malicious IP lists from the NTICS cloud service for use in network policy, virtual Deep Packet Inspection (vDPI) for payload pattern matching, and Advanced Threat Prevention combining IDS/IPS with network sandboxing, Network Traffic Analysis (NTA), and Network Detection and Response (NDR) correlation engines.
+To fully satisfy this control, organizations need to supplement VCF's built-in monitoring with processes for defining, curating, and updating IOC libraries. This typically involves integrating third-party threat intelligence feeds, establishing procedures for translating threat intelligence into detection rules across VCF Operations and network policy, and deploying a SIEM or endpoint detection platform to correlate VCF's telemetry with broader IOC databases.</t>
         </is>
       </c>
       <c r="G51" s="10" t="inlineStr">
@@ -5826,7 +5840,7 @@
       <c r="J61" s="10" t="inlineStr">
         <is>
           <t>VCF Protection and Recovery (PNR) provides data protection incident response capabilities through structured recovery plans, non-disruptive testing, and automated failover orchestration. Recovery plans define documented, repeatable response procedures that specify VM recovery sequences and reprotect operations following a recovery event, with reprotect process states displayed in the recovery plan user interface so operators can observe operation status. Test failover and planned migration operations validate response readiness before an incident, and disaster recovery failover handles unplanned events when the protected site is unavailable.
-PNR's event logging and alarm framework detects conditions that may indicate a data protection incident, including site connectivity loss, replication failures, and interrupted reprotect operations. PNR captures audit events that record user actions, including configuration changes and recovery plan executions, with the event name, user identity, and source IP address where the event was initiated. The PlanExecReprotectEnd event is signaled on the recovery site when a reprotect operation completes, supporting closure of the response lifecycle. Protection and Recovery Dashboards in VCF Operations provide consolidated visibility across vCenters, vSAN snapshot and replication sites, VMware Live Recovery Cloud regions, and protection and recovery site pairs to help incident responders see protection status at a glance.
+PNR's event logging and alarm framework detects conditions that may indicate a data protection incident, including site connectivity loss, replication failures, and interrupted reprotect operations. PNR captures audit events that record user actions, including configuration changes and recovery plan executions, with the event name, user identity, and source IP address where the event was initiated. The PlanExecReprotectEnd event is signaled on the recovery site when a reprotect operation completes, supporting closure of the response lifecycle. Protection and Recovery Dashboards in VCF Operations provide consolidated visibility across vCenters, vSAN snapshot and replication sites, VCF Protection and Recovery Cloud regions, and protection and recovery site pairs to help incident responders see protection status at a glance.
 For cyber-incident scenarios, PNR includes Cyber Recovery with a clean room at the recovery site to isolate recovered workloads during ransomware analysis. Cyber Recovery integrates with Carbon Black and CrowdStrike for security and vulnerability analysis: results include risk score details, environmental impact, CrowdScore severity (a CrowdScore of 100 indicates a critical threat level), and recommended remediation actions to support response decisions. When a disaster affects the management domain containing VCF Automation and VCF Operations, PNR enables service recovery in another management domain so organization users can return to running their workloads.</t>
         </is>
       </c>
